--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0232.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0232.xlsx
@@ -643,7 +643,7 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>Tiến độ của cậu sẽ được lưu khi thoát. Thoát ngay?
-&lt;color=#ac8839&gt;Bạn will continue from here when you come back.&lt;/color&gt;</t>
+&lt;color=#ac8839&gt;Cậu sẽ tiếp tục từ đây khi quay lại.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>Tiến độ sẽ không được lưu. Thoát ngay?
-&lt;color=#ac8839&gt;Any unsaved progress will be lost.&lt;/color&gt;</t>
+&lt;color=#ac8839&gt;Mọi tiến độ chưa lưu sẽ bị mất.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Nếu thoát bây giờ, tiến trình câu chuyện hiện tại sẽ bị dừng lại. Bạn có muốn thoát không?
-&lt;color=#ac8839&gt;Bạn may continue the story from the quest portal.&lt;/color&gt;</t>
+&lt;color=#ac8839&gt;Bạn có thể tiếp tục câu chuyện từ cổng nhiệm vụ.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>Nếu thoát bây giờ, tiến trình câu chuyện hiện tại sẽ bị dừng lại. Bạn có muốn thoát không?
-&lt;color=#ac8839&gt;Bạn may continue the story from the quest portal.&lt;/color&gt;</t>
+&lt;color=#ac8839&gt;Bạn có thể tiếp tục câu chuyện từ cổng nhiệm vụ.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>Sử dụng Dịch Chuyển Nhanh sẽ tạm dừng tiến trình câu chuyện hiện tại. Bạn có muốn rời đi không?
-&lt;color=#ac8839&gt;Bạn may continue the story from the quest portal.&lt;/color&gt;</t>
+&lt;color=#ac8839&gt;Bạn có thể tiếp tục câu chuyện từ cổng nhiệm vụ.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>Sử dụng Dịch Chuyển Nhanh sẽ tạm dừng tiến trình câu chuyện hiện tại. Bạn có muốn rời đi không?
-&lt;color=#ac8839&gt;Bạn may continue the story from the quest portal.&lt;/color&gt;</t>
+&lt;color=#ac8839&gt;Bạn có thể tiếp tục câu chuyện từ cổng nhiệm vụ.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Áp dụng cho tất cả Cộng Hưởng Giả?</t>
+          <t>Áp dụng cho tất cả Resonator?</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Insufficient storage space. Vui lòng giải phóng dung lượng và thử lại.</t>
+          <t>Không đủ dung lượng lưu trữ. Hãy giải phóng không gian và thử lại.</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Storage space available: {0}</t>
+          <t>Dung lượng lưu trữ khả dụng: {0}</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Không thể chọn do giới hạn loại vũ khí của Cộng Hưởng Giả.</t>
+          <t>Không thể chọn do giới hạn loại vũ khí của Resonator.</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Vui lòng khởi động lại ứng dụng để thay đổi có hiệu lực.</t>
+          <t>Vui lòng khởi động lại trò chơi để áp dụng thay đổi.</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Storage space required: {0}</t>
+          <t>Dung lượng lưu trữ cần thiết: {0}</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả này chưa trang bị Echo nào.</t>
+          <t>Resonator này chưa trang bị Echo nào.</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Tính năng đề xuất Tiếng Vang chưa được mở khóa.</t>
+          <t>Tính năng đề xuất Echo chưa được mở khóa.</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Bộ trang bị này đã được Cộng Hưởng Giả khác sử dụng.</t>
+          <t>Bộ trang bị này đã được Resonator khác sử dụng.</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Chưa chọn Tiếng Vang.</t>
+          <t>Chưa chọn Echo.</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Xác minh Điều Tiết Tiếng Vang thất bại.</t>
+          <t>Xác minh Điều Tiết Echo thất bại.</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả—Cấu hình Echo không khả dụng.</t>
+          <t>Resonator—Cấu hình Echo không khả dụng.</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Điều kiện Tiếng Vang chưa được đáp ứng.</t>
+          <t>Điều kiện Echo chưa được đáp ứng.</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Âm Hưởng Cộng Hưởng Giả Đã Bị Khóa</t>
+          <t>Âm Hưởng Resonator Đã Bị Khóa</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả—Cấu hình người chơi Echo không khả dụng.</t>
+          <t>Resonator—Cấu hình người chơi Echo không khả dụng.</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả đã bị khóa.</t>
+          <t>Resonator đã bị khóa.</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Không phân phối được phần thưởng Cộng Hưởng Giả</t>
+          <t>Không phân phối được phần thưởng Resonator</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Quá nhiều lần nhập liệu. Đợi chút rồi thử lại nhé, Rover!</t>
+          <t>Quá nhiều lần nhập liệu. Đợi chút rồi thử lại nhé, Vận Mệnh Giả!</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>R?i ?i à?</t>
+          <t>Cút đi à?</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Đội của bạn hiện có Cộng Hưởng Giả thử nghiệm. Không thể thay đổi ngoại hình của Rover.</t>
+          <t>Đội của bạn hiện có Resonator thử nghiệm. Không thể thay đổi ngoại hình của Rover.</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Sự kiện đã kết thúc. {Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} Xác nhận để thoát khỏi phiên bản.</t>
+          <t>Sự kiện đã kết thúc. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} Xác nhận để thoát khỏi phiên bản.</t>
         </is>
       </c>
     </row>
@@ -18731,7 +18731,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>&lt;color=#c15757ff&gt;Quest not accepted&lt;/color&gt;</t>
+          <t>&lt;color=#c15757ff&gt;Nhiệm vụ chưa được nhận&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Đã có Cộng Hưởng Giả Thử Nghiệm trong đội. Không thể mời thêm</t>
+          <t>Đã có Resonator Thử Nghiệm trong đội. Không thể mời thêm</t>
         </is>
       </c>
     </row>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Cậu muốn giảm độ khó không? {Cus:Ipt,Touch=tap PC=click Gamepad=press} để xác nhận.</t>
+          <t>Cậu muốn giảm độ khó không? {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xác nhận.</t>
         </is>
       </c>
     </row>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Đội của bạn hoặc đội của người chơi khác hiện có Cộng Hưởng Giả thử nghiệm. Không thể tham gia Chơi Cùng.</t>
+          <t>Đội của bạn hoặc đội của người chơi khác hiện có Resonator thử nghiệm. Không thể tham gia Chơi Cùng.</t>
         </is>
       </c>
     </row>
@@ -23738,7 +23738,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>&lt;color=#f9ffff&gt;Quantity&lt;/color&gt;: &lt;color=#f7eba6&gt;{0}&lt;/color&gt;</t>
+          <t>&lt;color=#f9ffff&gt;Số Lượng&lt;/color&gt;: &lt;color=#f7eba6&gt;{0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>&lt;color=#f9ffff99&gt;Total&lt;/color&gt;: &lt;color=#f9ffff&gt;{0}&lt;/color&gt;&lt;color=#f9ffff99&gt;/{1}&lt;/color&gt;</t>
+          <t>&lt;color=#f9ffff99&gt;Tổng&lt;/color&gt;: &lt;color=#f9ffff&gt;{0}&lt;/color&gt;&lt;color=#f9ffff99&gt;/{1}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23868,7 +23868,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>&lt;color=#f9ffff&gt;Proficiency&lt;/color&gt;: &lt;color=#f7eba6&gt;{0}&lt;/color&gt;</t>
+          <t>&lt;color=#f9ffff&gt;Độ Thành Thạo&lt;/color&gt;: &lt;color=#f7eba6&gt;{0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25363,7 +25363,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Sự kiện đã kết thúc. {Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} Xác nhận để thoát.</t>
+          <t>Sự kiện đã kết thúc. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} Xác nhận để thoát.</t>
         </is>
       </c>
     </row>
@@ -25885,7 +25885,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Total Points: {0}</t>
+          <t>Tổng Điểm: {0}</t>
         </is>
       </c>
     </row>
@@ -26730,7 +26730,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>{0}&lt;color=#bdcccc7f&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -27055,7 +27055,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro: Chiến Ca (Thứ Hai/Thứ Năm/Chủ Nhật)</t>
+          <t>Sonoro Sphere: Chiến Ca (Thứ Hai/Thứ Năm/Chủ Nhật)</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27120,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro: Chiến Ca (Thứ Ba/Thứ Sáu/Chủ Nhật)</t>
+          <t>Sonoro Sphere: Chiến Ca (Thứ Ba/Thứ Sáu/Chủ Nhật)</t>
         </is>
       </c>
     </row>
@@ -27185,7 +27185,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro: Chiến Ca (Thứ Tư/Thứ Bảy/Chủ Nhật)</t>
+          <t>Sonoro Sphere: Chiến Ca (Thứ Tư/Thứ Bảy/Chủ Nhật)</t>
         </is>
       </c>
     </row>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro: Gai (Thứ Hai/Thứ Năm/Chủ Nhật)</t>
+          <t>Sonoro Sphere: Gai (Thứ Hai/Thứ Năm/Chủ Nhật)</t>
         </is>
       </c>
     </row>
@@ -27510,7 +27510,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro: Gai (Thứ Ba/Thứ Sáu/Chủ Nhật)</t>
+          <t>Sonoro Sphere: Gai (Thứ Ba/Thứ Sáu/Chủ Nhật)</t>
         </is>
       </c>
     </row>
@@ -27575,7 +27575,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro: Gai (Thứ Tư/Thứ Bảy/Chủ Nhật)</t>
+          <t>Sonoro Sphere: Gai (Thứ Tư/Thứ Bảy/Chủ Nhật)</t>
         </is>
       </c>
     </row>
